--- a/planilha_produtos.xlsx
+++ b/planilha_produtos.xlsx
@@ -1,62 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe\Desktop\TRABALHO\automacao_kabana\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ad2da7471f08f19/Desktop/automy-canhoto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174435D0-CC2C-4C93-B6E1-2062E852AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{174435D0-CC2C-4C93-B6E1-2062E852AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49BC36E9-AB9F-48D9-A99B-472C387DBEED}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos Filtrados" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
-    <t>R$ 16,20</t>
-  </si>
-  <si>
-    <t>R$ 3,07</t>
-  </si>
-  <si>
-    <t>R$ 8,37</t>
-  </si>
-  <si>
-    <t>R$ 1,39</t>
-  </si>
-  <si>
-    <t>R$ 11,46</t>
-  </si>
-  <si>
-    <t>R$ 7,71</t>
-  </si>
-  <si>
-    <t>R$ 5,14</t>
-  </si>
-  <si>
-    <t>R$ 5,65</t>
-  </si>
-  <si>
-    <t>R$ 223,25</t>
-  </si>
-  <si>
-    <t>R$ 19,99</t>
-  </si>
-  <si>
     <t>CODIGO DO PRODUTO</t>
   </si>
   <si>
@@ -64,13 +29,47 @@
   </si>
   <si>
     <t>QUANTIDADE ESTOQUE</t>
+  </si>
+  <si>
+    <t>16.20</t>
+  </si>
+  <si>
+    <t>3.07</t>
+  </si>
+  <si>
+    <t>8.37</t>
+  </si>
+  <si>
+    <t>1.39</t>
+  </si>
+  <si>
+    <t>11.46</t>
+  </si>
+  <si>
+    <t>7.71</t>
+  </si>
+  <si>
+    <t>5.14</t>
+  </si>
+  <si>
+    <t>5.65</t>
+  </si>
+  <si>
+    <t>223.25</t>
+  </si>
+  <si>
+    <t>19.99</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +81,21 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,16 +118,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -195,12 +218,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{437D60C4-A60C-4F86-B477-6474C043A317}" name="Tabela1" displayName="Tabela1" ref="A1:C13" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{437D60C4-A60C-4F86-B477-6474C043A317}" name="Tabela1" displayName="Tabela1" ref="A1:C13" totalsRowShown="0" dataDxfId="3">
   <autoFilter ref="A1:C13" xr:uid="{437D60C4-A60C-4F86-B477-6474C043A317}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2044C3A8-FB9C-4E17-89F2-61FD516B133A}" name="CODIGO DO PRODUTO" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{BB4207D8-AEF9-4F1D-ABE6-B2097DED2E44}" name="VALOR PRODUTO" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{8875537E-C0D7-498E-BC79-D5786176594E}" name="QUANTIDADE ESTOQUE" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{2044C3A8-FB9C-4E17-89F2-61FD516B133A}" name="CODIGO DO PRODUTO" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{BB4207D8-AEF9-4F1D-ABE6-B2097DED2E44}" name="VALOR PRODUTO" dataDxfId="1" dataCellStyle="Moeda"/>
+    <tableColumn id="3" xr3:uid="{8875537E-C0D7-498E-BC79-D5786176594E}" name="QUANTIDADE ESTOQUE" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -491,161 +514,165 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>373</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>96</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>255</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>2</v>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C4" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>262</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>98</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>254</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>212</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C8" s="1">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>213</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>6</v>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C9" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>214</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C10" s="1">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>215</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>76</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C12" s="1">
         <v>2508</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>100</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C13" s="1">
         <v>137</v>
       </c>
     </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="154" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/planilha_produtos.xlsx
+++ b/planilha_produtos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ad2da7471f08f19/Desktop/automy-canhoto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{174435D0-CC2C-4C93-B6E1-2062E852AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49BC36E9-AB9F-48D9-A99B-472C387DBEED}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{174435D0-CC2C-4C93-B6E1-2062E852AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09C519A-1126-4A7F-9C7E-D1084235585F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>CODIGO DO PRODUTO</t>
   </si>
@@ -31,28 +31,10 @@
     <t>QUANTIDADE ESTOQUE</t>
   </si>
   <si>
-    <t>16.20</t>
-  </si>
-  <si>
-    <t>3.07</t>
-  </si>
-  <si>
-    <t>8.37</t>
-  </si>
-  <si>
-    <t>1.39</t>
-  </si>
-  <si>
-    <t>11.46</t>
-  </si>
-  <si>
     <t>7.71</t>
   </si>
   <si>
     <t>5.14</t>
-  </si>
-  <si>
-    <t>5.65</t>
   </si>
   <si>
     <t>223.25</t>
@@ -534,77 +516,41 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>373</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>331</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>96</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1">
-        <v>31</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>255</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>7</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>262</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1">
-        <v>63</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>98</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1">
-        <v>20</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>254</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1">
-        <v>7</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>212</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <v>111</v>
@@ -615,40 +561,28 @@
         <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>214</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1">
-        <v>131</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>215</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1">
         <v>2508</v>
@@ -659,7 +593,7 @@
         <v>100</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1">
         <v>137</v>

--- a/planilha_produtos.xlsx
+++ b/planilha_produtos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ad2da7471f08f19/Desktop/automy-canhoto/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7AD2DA7471F08F19/Desktop/automy-canhoto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{174435D0-CC2C-4C93-B6E1-2062E852AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09C519A-1126-4A7F-9C7E-D1084235585F}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{174435D0-CC2C-4C93-B6E1-2062E852AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C0729E9-5934-43A2-972C-2B0112CEBFE2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="2550" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos Filtrados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>CODIGO DO PRODUTO</t>
   </si>
@@ -31,16 +31,7 @@
     <t>QUANTIDADE ESTOQUE</t>
   </si>
   <si>
-    <t>7.71</t>
-  </si>
-  <si>
-    <t>5.14</t>
-  </si>
-  <si>
     <t>223.25</t>
-  </si>
-  <si>
-    <t>19.99</t>
   </si>
 </sst>
 </file>
@@ -546,26 +537,14 @@
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>212</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>111</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>213</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1">
-        <v>48</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -582,22 +561,16 @@
         <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1">
         <v>2508</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>100</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1">
-        <v>137</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
